--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_32_R4.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_32_R4.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.4828</v>
+        <v>7.5336</v>
       </c>
       <c r="E2" t="n">
-        <v>3.3003</v>
+        <v>3.4182</v>
       </c>
       <c r="F2" t="n">
-        <v>4.1826</v>
+        <v>4.1154</v>
       </c>
       <c r="G2" t="n">
         <v>3.5693</v>
@@ -610,13 +610,13 @@
         <v>2.3195</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.9963</v>
+        <v>-0.9456</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.4007</v>
+        <v>-0.2827</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5957</v>
+        <v>-0.6629</v>
       </c>
       <c r="V2" t="n">
         <v>2.8223</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.4768</v>
+        <v>3.7806</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.8626</v>
+        <v>-0.3908</v>
       </c>
       <c r="F3" t="n">
-        <v>4.3394</v>
+        <v>4.1714</v>
       </c>
       <c r="G3" t="n">
         <v>0.2441</v>
@@ -688,13 +688,13 @@
         <v>1.8556</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0883</v>
+        <v>0.3921</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.8804</v>
+        <v>-0.4086</v>
       </c>
       <c r="U3" t="n">
-        <v>0.9687</v>
+        <v>0.8006</v>
       </c>
       <c r="V3" t="n">
         <v>2.6805</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.6226</v>
+        <v>2.6122</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5199</v>
+        <v>0.2407</v>
       </c>
       <c r="F4" t="n">
-        <v>2.1027</v>
+        <v>2.3715</v>
       </c>
       <c r="G4" t="n">
         <v>1.2365</v>
@@ -766,13 +766,13 @@
         <v>1.3917</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1362</v>
+        <v>0.1259</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1019</v>
+        <v>-0.3811</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2381</v>
+        <v>0.507</v>
       </c>
       <c r="V4" t="n">
         <v>-0.1418</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>L. KRATZER</t>
+          <t>J. HOLLATZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6279</v>
+        <v>1.739</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2067</v>
+        <v>0.3133</v>
       </c>
       <c r="F5" t="n">
-        <v>1.4211</v>
+        <v>1.4257</v>
       </c>
       <c r="G5" t="n">
-        <v>1.457</v>
+        <v>-0.1863</v>
       </c>
       <c r="H5" t="n">
-        <v>1.2629</v>
+        <v>-0.2064</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1941</v>
+        <v>0.0201</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3561</v>
+        <v>-0.3934</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3193</v>
+        <v>-0.4671</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0368</v>
+        <v>0.0736</v>
       </c>
       <c r="M5" t="n">
-        <v>1.1009</v>
+        <v>0.2071</v>
       </c>
       <c r="N5" t="n">
-        <v>0.9436</v>
+        <v>0.2606</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1573</v>
+        <v>-0.0535</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>0.9278</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>0.9278</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1709</v>
+        <v>-0.0747</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1494</v>
+        <v>-0.3655</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3203</v>
+        <v>0.2908</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. HOLLATZ</t>
+          <t>L. KRATZER</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3208</v>
+        <v>1.6957</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1639</v>
+        <v>0.4426</v>
       </c>
       <c r="F6" t="n">
-        <v>1.1569</v>
+        <v>1.2531</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.1863</v>
+        <v>1.457</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.2064</v>
+        <v>1.2629</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0201</v>
+        <v>0.1941</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.3934</v>
+        <v>0.3561</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.4671</v>
+        <v>0.3193</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0736</v>
+        <v>0.0368</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2071</v>
+        <v>1.1009</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2606</v>
+        <v>0.9436</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.0535</v>
+        <v>0.1573</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9278</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9278</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4929</v>
+        <v>0.2388</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5149</v>
+        <v>0.08649999999999999</v>
       </c>
       <c r="U6" t="n">
-        <v>0.022</v>
+        <v>0.1522</v>
       </c>
       <c r="V6" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5357</v>
+        <v>0.4252</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.3371</v>
+        <v>-0.3803</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8727</v>
+        <v>0.8055</v>
       </c>
       <c r="G7" t="n">
         <v>3.5087</v>
@@ -1000,13 +1000,13 @@
         <v>2.0876</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.9883999999999999</v>
+        <v>-1.0989</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1766</v>
+        <v>-0.2199</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.8118</v>
+        <v>-0.879</v>
       </c>
       <c r="V7" t="n">
         <v>-2.6805</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>W. GABRIEL</t>
+          <t>K. BALDWIN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2487</v>
+        <v>-0.2338</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.2268</v>
+        <v>-4.2558</v>
       </c>
       <c r="F8" t="n">
-        <v>2.4755</v>
+        <v>4.022</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8300999999999999</v>
+        <v>-0.1226</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.5485</v>
+        <v>0.54</v>
       </c>
       <c r="I8" t="n">
-        <v>1.3786</v>
+        <v>-0.6626</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2693</v>
+        <v>-2.5814</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.43</v>
+        <v>-0.4531</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6993</v>
+        <v>-2.1283</v>
       </c>
       <c r="M8" t="n">
-        <v>0.5607</v>
+        <v>2.4587</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.1186</v>
+        <v>0.9931</v>
       </c>
       <c r="O8" t="n">
-        <v>0.6793</v>
+        <v>1.4657</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.6959</v>
+        <v>0.9278</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.5515</v>
+        <v>-1.3917</v>
       </c>
       <c r="R8" t="n">
-        <v>1.8556</v>
+        <v>2.3195</v>
       </c>
       <c r="S8" t="n">
-        <v>0.6506</v>
+        <v>-1.0389</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0553</v>
+        <v>-0.2827</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5953000000000001</v>
+        <v>-0.7562</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.3507</v>
+        <v>-0.2685</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.0221</v>
+        <v>-0.8727</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6714</v>
+        <v>0.6041</v>
       </c>
       <c r="G9" t="n">
         <v>-0.3188</v>
@@ -1156,13 +1156,13 @@
         <v>1.1598</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1195</v>
+        <v>-0.0373</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6642</v>
+        <v>-0.5149</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5447</v>
+        <v>0.4775</v>
       </c>
       <c r="V9" t="n">
         <v>-1.0722</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>K. BALDWIN</t>
+          <t>W. GABRIEL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.4525</v>
+        <v>-0.2732</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.3737</v>
+        <v>-2.5806</v>
       </c>
       <c r="F10" t="n">
-        <v>3.9212</v>
+        <v>2.3075</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.1226</v>
+        <v>0.8300999999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>0.54</v>
+        <v>-0.5485</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.6626</v>
+        <v>1.3786</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.5814</v>
+        <v>0.2693</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.4531</v>
+        <v>-0.43</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.1283</v>
+        <v>0.6993</v>
       </c>
       <c r="M10" t="n">
-        <v>2.4587</v>
+        <v>0.5607</v>
       </c>
       <c r="N10" t="n">
-        <v>0.9931</v>
+        <v>-0.1186</v>
       </c>
       <c r="O10" t="n">
-        <v>1.4657</v>
+        <v>0.6793</v>
       </c>
       <c r="P10" t="n">
-        <v>0.9278</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.3917</v>
+        <v>-2.5515</v>
       </c>
       <c r="R10" t="n">
-        <v>2.3195</v>
+        <v>1.8556</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.2577</v>
+        <v>0.1287</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4007</v>
+        <v>-0.2985</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.8571</v>
+        <v>0.4272</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.1906</v>
+        <v>-1.1935</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.1479</v>
+        <v>-2.3524</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9573</v>
+        <v>1.1589</v>
       </c>
       <c r="G11" t="n">
         <v>1.1923</v>
@@ -1312,13 +1312,13 @@
         <v>1.6237</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.151</v>
+        <v>-1.1538</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1845</v>
+        <v>-0.389</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.9665</v>
+        <v>-0.7648</v>
       </c>
       <c r="V11" t="n">
         <v>-0.5361</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.8572</v>
+        <v>-4.6064</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.697</v>
+        <v>-5.3117</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8398</v>
+        <v>0.7054</v>
       </c>
       <c r="G12" t="n">
         <v>-2.7442</v>
@@ -1390,13 +1390,13 @@
         <v>1.8556</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.8784</v>
+        <v>-1.6276</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.1202</v>
+        <v>-0.735</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.7582</v>
+        <v>-0.8927</v>
       </c>
       <c r="V12" t="n">
         <v>-0.9304</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>10.4643</v>
+        <v>11.2109</v>
       </c>
       <c r="E13" t="n">
-        <v>-12.4764</v>
+        <v>-11.7295</v>
       </c>
       <c r="F13" t="n">
-        <v>22.9406</v>
+        <v>22.9405</v>
       </c>
       <c r="G13" t="n">
         <v>8.6661</v>
@@ -1438,13 +1438,13 @@
         <v>5.5044</v>
       </c>
       <c r="I13" t="n">
-        <v>3.161799999999999</v>
+        <v>3.1618</v>
       </c>
       <c r="J13" t="n">
         <v>-3.8229</v>
       </c>
       <c r="K13" t="n">
-        <v>0.07609999999999967</v>
+        <v>0.07609999999999978</v>
       </c>
       <c r="L13" t="n">
         <v>-3.8992</v>
@@ -1459,7 +1459,7 @@
         <v>7.0608</v>
       </c>
       <c r="P13" t="n">
-        <v>6.958600000000001</v>
+        <v>6.9586</v>
       </c>
       <c r="Q13" t="n">
         <v>-10.4379</v>
@@ -1468,19 +1468,19 @@
         <v>17.3964</v>
       </c>
       <c r="S13" t="n">
-        <v>-5.838200000000001</v>
+        <v>-5.0913</v>
       </c>
       <c r="T13" t="n">
-        <v>-4.5382</v>
+        <v>-3.7914</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.3002</v>
+        <v>-1.3003</v>
       </c>
       <c r="V13" t="n">
-        <v>0.6779000000000001</v>
+        <v>0.6778999999999992</v>
       </c>
       <c r="W13" t="n">
-        <v>6.3225</v>
+        <v>6.322499999999999</v>
       </c>
       <c r="X13" t="n">
         <v>-5.644600000000001</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.3292</v>
+        <v>5.0608</v>
       </c>
       <c r="E14" t="n">
-        <v>4.8184</v>
+        <v>2.6953</v>
       </c>
       <c r="F14" t="n">
-        <v>2.5107</v>
+        <v>2.3656</v>
       </c>
       <c r="G14" t="n">
         <v>0.3988</v>
@@ -1546,13 +1546,13 @@
         <v>1.8556</v>
       </c>
       <c r="S14" t="n">
-        <v>4.8582</v>
+        <v>2.5899</v>
       </c>
       <c r="T14" t="n">
-        <v>3.5311</v>
+        <v>1.4079</v>
       </c>
       <c r="U14" t="n">
-        <v>1.3271</v>
+        <v>1.1819</v>
       </c>
       <c r="V14" t="n">
         <v>1.6083</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>O. DIOP</t>
+          <t>S. SHIELDS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6268</v>
+        <v>1.4874</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.0579</v>
+        <v>-1.3504</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6846</v>
+        <v>2.8378</v>
       </c>
       <c r="G15" t="n">
-        <v>0.3206</v>
+        <v>-1.6752</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1633</v>
+        <v>-1.8558</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1573</v>
+        <v>0.1806</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0168</v>
+        <v>-2.2646</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0168</v>
+        <v>-1.4012</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>-0.8635</v>
       </c>
       <c r="M15" t="n">
-        <v>0.3038</v>
+        <v>0.5894</v>
       </c>
       <c r="N15" t="n">
-        <v>0.1465</v>
+        <v>-0.4547</v>
       </c>
       <c r="O15" t="n">
-        <v>0.1573</v>
+        <v>1.0441</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.3917</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-0.232</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.6237</v>
       </c>
       <c r="S15" t="n">
-        <v>0.3062</v>
+        <v>1.093</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.0747</v>
+        <v>0.4683</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3809</v>
+        <v>0.6247</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S. SHIELDS</t>
+          <t>O. DIOP</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3865</v>
+        <v>0.5259</v>
       </c>
       <c r="E16" t="n">
-        <v>-2.294</v>
+        <v>-0.0579</v>
       </c>
       <c r="F16" t="n">
-        <v>2.6805</v>
+        <v>0.5838</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.6752</v>
+        <v>0.3206</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.8558</v>
+        <v>0.1633</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1806</v>
+        <v>0.1573</v>
       </c>
       <c r="J16" t="n">
-        <v>-2.2646</v>
+        <v>0.0168</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.4012</v>
+        <v>0.0168</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.8635</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0.5894</v>
+        <v>0.3038</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.4547</v>
+        <v>0.1465</v>
       </c>
       <c r="O16" t="n">
-        <v>1.0441</v>
+        <v>0.1573</v>
       </c>
       <c r="P16" t="n">
-        <v>1.3917</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.232</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.6237</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.007900000000000001</v>
+        <v>0.2054</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4753</v>
+        <v>-0.0747</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4674</v>
+        <v>0.2801</v>
       </c>
       <c r="V16" t="n">
-        <v>0.6778999999999999</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>0.6778999999999999</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.3397</v>
+        <v>-0.1152</v>
       </c>
       <c r="E17" t="n">
         <v>-0.0742</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2655</v>
+        <v>-0.0411</v>
       </c>
       <c r="G17" t="n">
         <v>0.9171</v>
@@ -1780,13 +1780,13 @@
         <v>0.4639</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1125</v>
+        <v>0.112</v>
       </c>
       <c r="T17" t="n">
         <v>-0.4481</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3356</v>
+        <v>0.5601</v>
       </c>
       <c r="V17" t="n">
         <v>-1.6083</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>B. DUNSTON</t>
+          <t>A. BROOKS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.5252</v>
+        <v>-0.3721</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.4355</v>
+        <v>-2.4656</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.0896</v>
+        <v>2.0935</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.6385</v>
+        <v>0.0479</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.9363</v>
+        <v>-1.0229</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2978</v>
+        <v>1.0707</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.6991000000000001</v>
+        <v>-1.6245</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.7359</v>
+        <v>-1.2296</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0368</v>
+        <v>-0.3949</v>
       </c>
       <c r="M18" t="n">
-        <v>0.0606</v>
+        <v>1.6724</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2004</v>
+        <v>0.2067</v>
       </c>
       <c r="O18" t="n">
-        <v>0.261</v>
+        <v>1.4657</v>
       </c>
       <c r="P18" t="n">
-        <v>0.232</v>
+        <v>0.6959</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.232</v>
+        <v>0.6959</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1186</v>
+        <v>0.0982</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2636</v>
+        <v>-0.841</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3822</v>
+        <v>0.9392</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-1.214</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. BROOKS</t>
+          <t>N. MANNION</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.7716</v>
+        <v>-0.6279</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.8194</v>
+        <v>-0.7973</v>
       </c>
       <c r="F19" t="n">
-        <v>2.0478</v>
+        <v>0.1693</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0479</v>
+        <v>1.2875</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.0229</v>
+        <v>0.8859</v>
       </c>
       <c r="I19" t="n">
-        <v>1.0707</v>
+        <v>0.4016</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.6245</v>
+        <v>0.8300999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.2296</v>
+        <v>0.7933</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.3949</v>
+        <v>0.0368</v>
       </c>
       <c r="M19" t="n">
-        <v>1.6724</v>
+        <v>0.4574</v>
       </c>
       <c r="N19" t="n">
-        <v>0.2067</v>
+        <v>0.0926</v>
       </c>
       <c r="O19" t="n">
-        <v>1.4657</v>
+        <v>0.3648</v>
       </c>
       <c r="P19" t="n">
-        <v>0.6959</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R19" t="n">
-        <v>0.6959</v>
+        <v>0.4639</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3014</v>
+        <v>-0.1474</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.1949</v>
+        <v>-0.4676</v>
       </c>
       <c r="U19" t="n">
-        <v>0.8935</v>
+        <v>0.3203</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.214</v>
+        <v>-1.0722</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.214</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>N. MANNION</t>
+          <t>B. DUNSTON</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.4751</v>
+        <v>-0.7053</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.1511</v>
+        <v>-0.9074</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.324</v>
+        <v>0.2021</v>
       </c>
       <c r="G20" t="n">
-        <v>1.2875</v>
+        <v>-0.6385</v>
       </c>
       <c r="H20" t="n">
-        <v>0.8859</v>
+        <v>-0.9363</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4016</v>
+        <v>0.2978</v>
       </c>
       <c r="J20" t="n">
-        <v>0.8300999999999999</v>
+        <v>-0.6991000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>0.7933</v>
+        <v>-0.7359</v>
       </c>
       <c r="L20" t="n">
         <v>0.0368</v>
       </c>
       <c r="M20" t="n">
-        <v>0.4574</v>
+        <v>0.0606</v>
       </c>
       <c r="N20" t="n">
-        <v>0.0926</v>
+        <v>-0.2004</v>
       </c>
       <c r="O20" t="n">
-        <v>0.3648</v>
+        <v>0.261</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.6959</v>
+        <v>0.232</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.4639</v>
+        <v>0.232</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.9946</v>
+        <v>-0.2987</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8215</v>
+        <v>-0.2082</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1731</v>
+        <v>-0.0905</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.5466</v>
+        <v>-2.2213</v>
       </c>
       <c r="E21" t="n">
         <v>-3.921</v>
       </c>
       <c r="F21" t="n">
-        <v>1.3744</v>
+        <v>1.6997</v>
       </c>
       <c r="G21" t="n">
         <v>-1.1543</v>
@@ -2092,13 +2092,13 @@
         <v>1.1598</v>
       </c>
       <c r="S21" t="n">
-        <v>0.7648</v>
+        <v>1.0901</v>
       </c>
       <c r="T21" t="n">
         <v>0.7512</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0136</v>
+        <v>0.3389</v>
       </c>
       <c r="V21" t="n">
         <v>0.3943</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.8899</v>
+        <v>-2.5797</v>
       </c>
       <c r="E22" t="n">
-        <v>-6.0583</v>
+        <v>-5.4685</v>
       </c>
       <c r="F22" t="n">
-        <v>3.1684</v>
+        <v>2.8888</v>
       </c>
       <c r="G22" t="n">
         <v>-2.9354</v>
@@ -2170,13 +2170,13 @@
         <v>1.6237</v>
       </c>
       <c r="S22" t="n">
-        <v>1.0609</v>
+        <v>1.3711</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1766</v>
+        <v>0.4132</v>
       </c>
       <c r="U22" t="n">
-        <v>1.2375</v>
+        <v>0.9579</v>
       </c>
       <c r="V22" t="n">
         <v>1.0722</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.7183</v>
+        <v>-3.0277</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.5276</v>
+        <v>-3.9378</v>
       </c>
       <c r="F23" t="n">
-        <v>0.8093</v>
+        <v>0.9101</v>
       </c>
       <c r="G23" t="n">
         <v>-3.4894</v>
@@ -2248,13 +2248,13 @@
         <v>1.1598</v>
       </c>
       <c r="S23" t="n">
-        <v>0.2324</v>
+        <v>0.923</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.0272</v>
+        <v>0.5625</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2596</v>
+        <v>0.3605</v>
       </c>
       <c r="V23" t="n">
         <v>0.9304</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.5402</v>
+        <v>-6.3163</v>
       </c>
       <c r="E24" t="n">
-        <v>-6.4199</v>
+        <v>-6.6558</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.1203</v>
+        <v>0.3394</v>
       </c>
       <c r="G24" t="n">
         <v>-1.7451</v>
@@ -2326,13 +2326,13 @@
         <v>1.1598</v>
       </c>
       <c r="S24" t="n">
-        <v>0.1507</v>
+        <v>0.3745</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.0272</v>
+        <v>-0.2631</v>
       </c>
       <c r="U24" t="n">
-        <v>0.1779</v>
+        <v>0.6375999999999999</v>
       </c>
       <c r="V24" t="n">
         <v>-1.4665</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-10.4641</v>
+        <v>-8.891399999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>-22.9405</v>
+        <v>-22.9406</v>
       </c>
       <c r="F25" t="n">
-        <v>12.4763</v>
+        <v>14.049</v>
       </c>
       <c r="G25" t="n">
         <v>-8.666</v>
@@ -2404,13 +2404,13 @@
         <v>10.4381</v>
       </c>
       <c r="S25" t="n">
-        <v>5.838200000000001</v>
+        <v>7.411100000000001</v>
       </c>
       <c r="T25" t="n">
         <v>1.3004</v>
       </c>
       <c r="U25" t="n">
-        <v>4.5378</v>
+        <v>6.1107</v>
       </c>
       <c r="V25" t="n">
         <v>-0.6779000000000001</v>
